--- a/Excel Class Files/Part 1 Introduction to excel.xlsx
+++ b/Excel Class Files/Part 1 Introduction to excel.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Desktop\New excel class\Class file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Documents\GitHub\Free_Datasets\Excel Class Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFB982D-D8BF-4C56-AF9F-ECAE1993014C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F388D6-39E7-42F9-AC18-2692BFAE99C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
     <sheet name="Worksheet components" sheetId="3" r:id="rId2"/>
     <sheet name="Nevigation" sheetId="4" r:id="rId3"/>
-    <sheet name="Data Entry" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_Hlk177396450" localSheetId="0">Introduction!$M$108</definedName>
@@ -37,9 +36,6 @@
   </si>
   <si>
     <t>Price</t>
-  </si>
-  <si>
-    <t>Orderamount</t>
   </si>
   <si>
     <t>Sales</t>
@@ -72,14 +68,17 @@
     <t>Nintendo</t>
   </si>
   <si>
-    <t>Use Comparison operator here.</t>
+    <t>Learn to Nevigate in a Sheet.</t>
+  </si>
+  <si>
+    <t>QTY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,8 +94,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -115,8 +122,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -165,48 +178,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -214,15 +190,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1244,89 +1215,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>388938</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47626</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>36512</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>52388</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>107951</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>115888</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Scroll: Horizontal 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="388938" y="238126"/>
-          <a:ext cx="3386138" cy="830262"/>
-        </a:xfrm>
-        <a:prstGeom prst="horizontalScroll">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent4">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1800" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Learn to Nevigate in a Sheet.</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>417513</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>36513</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>174625</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>7938</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>500062</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>23813</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1341,7 +1239,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1028701" y="4989513"/>
+          <a:off x="4314825" y="2632076"/>
           <a:ext cx="3424237" cy="733425"/>
         </a:xfrm>
         <a:prstGeom prst="horizontalScroll">
@@ -1403,16 +1301,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>23812</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>158751</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>238124</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>119063</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>587374</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>47626</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1427,8 +1325,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="992188" y="3587750"/>
-          <a:ext cx="3524249" cy="1103313"/>
+          <a:off x="4302125" y="1785939"/>
+          <a:ext cx="3524249" cy="841375"/>
         </a:xfrm>
         <a:prstGeom prst="horizontalScroll">
           <a:avLst/>
@@ -1500,16 +1398,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>409576</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>115888</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>63501</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>68262</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>34926</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1524,8 +1422,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1019176" y="1428750"/>
-          <a:ext cx="2295524" cy="733425"/>
+          <a:off x="4394201" y="357189"/>
+          <a:ext cx="2301874" cy="733425"/>
         </a:xfrm>
         <a:prstGeom prst="horizontalScroll">
           <a:avLst/>
@@ -1586,16 +1484,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>392114</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>60325</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>58739</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>87314</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>460376</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1610,7 +1508,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1003302" y="2536825"/>
+          <a:off x="4337052" y="1084263"/>
           <a:ext cx="2751137" cy="733425"/>
         </a:xfrm>
         <a:prstGeom prst="horizontalScroll">
@@ -1668,582 +1566,6 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>394608</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>55563</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>579438</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>142874</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="Scroll: Horizontal 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="394608" y="1198563"/>
-          <a:ext cx="5685518" cy="3516311"/>
-        </a:xfrm>
-        <a:prstGeom prst="horizontalScroll">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent4">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>1. </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Arithmetic operators in Excel are used to perform basic mathematical calculations.</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>214314</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>11909</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>71440</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Callout: Left Arrow 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2035970" y="202409"/>
-          <a:ext cx="2309811" cy="1202531"/>
-        </a:xfrm>
-        <a:prstGeom prst="leftArrowCallout">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="1"/>
-            <a:t>1. Use these cells to enter any</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="1" baseline="0"/>
-            <a:t> Information you like to store to store it ex. Name, Age, Marks, Numbers etc</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="1"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>416719</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>92924</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>311943</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>160789</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Callout: Left Arrow 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2250282" y="5045924"/>
-          <a:ext cx="2339974" cy="1401365"/>
-        </a:xfrm>
-        <a:prstGeom prst="leftArrowCallout">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent5">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent5"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent5"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" i="1">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>2</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>. You can do Calculation on numbers using a ' = ' Equal operator at the start and use arithmatic operators</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>    ( +, -, *, / ) to calculate.</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="1">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>384970</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>19334</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>460375</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>150813</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Scroll: Horizontal 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4663283" y="4972334"/>
-          <a:ext cx="2520155" cy="1083979"/>
-        </a:xfrm>
-        <a:prstGeom prst="horizontalScroll">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent4">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>NOTE : A ' = ' is a special kind of charecter which is used to write a function, perform calculations</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>, or references to other cells.</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>354078</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>101147</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>323994</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>154358</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="965266" y="2196647"/>
-          <a:ext cx="4859416" cy="1767711"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>467179</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>112259</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>39688</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>9070</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="Scroll: Horizontal 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="467179" y="6779759"/>
-          <a:ext cx="5695723" cy="3516311"/>
-        </a:xfrm>
-        <a:prstGeom prst="horizontalScroll">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent4">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>2. </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Comparison operators in Excel are </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>used to compare values</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> and determine their</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>relationships. </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>They return a Boolean result (TRUE or FALSE)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> based on the comparison.</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>416151</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>36334</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>455839</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>171412</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1028472" y="8037334"/>
-          <a:ext cx="4938260" cy="1468578"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2631,311 +1953,176 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{767BE984-796B-4F83-AD68-B2860F3BD472}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="I4:M12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="4" max="4" width="10.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
     <col min="9" max="9" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.42578125" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I4" s="6" t="s">
+    <row r="1" spans="1:6" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="D3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="6" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
+      <c r="C4" s="5">
+        <v>450</v>
+      </c>
+      <c r="D4" s="5">
+        <v>7</v>
+      </c>
+      <c r="E4" s="5">
+        <v>3150</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="5" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I5" s="5" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5">
+        <v>450</v>
+      </c>
+      <c r="D5" s="5">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5">
+        <v>3150</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="5">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="5">
+        <v>350</v>
+      </c>
+      <c r="D6" s="5">
+        <v>5</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1750</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="5">
+        <v>700</v>
+      </c>
+      <c r="D7" s="5">
+        <v>7</v>
+      </c>
+      <c r="E7" s="5">
+        <v>4900</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5">
         <v>450</v>
       </c>
-      <c r="K5" s="5">
+      <c r="D8" s="5">
+        <v>3</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1350</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="5">
+        <v>425</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5">
+        <v>850</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5">
+        <v>450</v>
+      </c>
+      <c r="D10" s="5">
+        <v>4</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1800</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="5">
+        <v>300</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5">
+        <v>300</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="L5" s="5">
-        <v>3150</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J6" s="5">
-        <v>450</v>
-      </c>
-      <c r="K6" s="5">
-        <v>7</v>
-      </c>
-      <c r="L6" s="5">
-        <v>3150</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J7" s="5">
-        <v>350</v>
-      </c>
-      <c r="K7" s="5">
-        <v>5</v>
-      </c>
-      <c r="L7" s="5">
-        <v>1750</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="5">
-        <v>700</v>
-      </c>
-      <c r="K8" s="5">
-        <v>7</v>
-      </c>
-      <c r="L8" s="5">
-        <v>4900</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="5">
-        <v>450</v>
-      </c>
-      <c r="K9" s="5">
-        <v>3</v>
-      </c>
-      <c r="L9" s="5">
-        <v>1350</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I10" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="5">
-        <v>425</v>
-      </c>
-      <c r="K10" s="5">
-        <v>2</v>
-      </c>
-      <c r="L10" s="5">
-        <v>850</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J11" s="5">
-        <v>450</v>
-      </c>
-      <c r="K11" s="5">
-        <v>4</v>
-      </c>
-      <c r="L11" s="5">
-        <v>1800</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="5">
-        <v>300</v>
-      </c>
-      <c r="K12" s="5">
-        <v>1</v>
-      </c>
-      <c r="L12" s="5">
-        <v>300</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35B2B0D7-B7DC-4E15-A877-15CC6CE7494E}">
-  <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:I65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-    </row>
-    <row r="56" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C56" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="I56" s="9"/>
-    </row>
-    <row r="57" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
-    </row>
-    <row r="58" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
-      <c r="I58" s="5"/>
-    </row>
-    <row r="59" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
-      <c r="I59" s="5"/>
-    </row>
-    <row r="60" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
-    </row>
-    <row r="61" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
-    </row>
-    <row r="62" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
-    </row>
-    <row r="63" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-    </row>
-    <row r="64" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
-    </row>
-    <row r="65" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C56:I56"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>